--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_los_rios.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:55</t>
+    <t xml:space="preserve">2026-09-09 21:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_los_rios.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:03</t>
+    <t xml:space="preserve">2026-09-18 10:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -892,7 +892,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -901,12 +901,12 @@
         <v>26</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>33.05</v>
+        <v>36.81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -915,12 +915,12 @@
         <v>27</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>67.04</v>
+        <v>71.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -929,12 +929,12 @@
         <v>28</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>94.53</v>
+        <v>93.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -943,12 +943,12 @@
         <v>26</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>36.81</v>
+        <v>33.05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>3</v>
@@ -957,12 +957,12 @@
         <v>27</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>71.64</v>
+        <v>67.04</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>3</v>
@@ -971,12 +971,12 @@
         <v>28</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>93.49</v>
+        <v>94.53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>6</v>
@@ -985,12 +985,12 @@
         <v>29</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>95.54</v>
+        <v>94.93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
@@ -999,12 +999,12 @@
         <v>30</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>97.79</v>
+        <v>96.79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>6</v>
@@ -1013,12 +1013,12 @@
         <v>29</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>94.93</v>
+        <v>95.54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>6</v>
@@ -1027,12 +1027,12 @@
         <v>30</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>96.79</v>
+        <v>97.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
@@ -1041,12 +1041,12 @@
         <v>31</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>92.05</v>
+        <v>91.28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>7</v>
@@ -1055,12 +1055,12 @@
         <v>32</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>89.19</v>
+        <v>88.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
@@ -1069,12 +1069,12 @@
         <v>31</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>91.28</v>
+        <v>92.05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>7</v>
@@ -1083,7 +1083,7 @@
         <v>32</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>88.54</v>
+        <v>89.19</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_los_rios.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:52</t>
+    <t xml:space="preserve">2026-09-23 16:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_los_rios.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 16:36</t>
+    <t xml:space="preserve">2026-10-05 06:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
